--- a/src/test/resources/testScriptData.xlsx
+++ b/src/test/resources/testScriptData.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Automation Testing\Selenium\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5220CC13-AFAE-4448-A844-E42A9E282346}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02B07A4D-DEB8-4B32-8503-BF328361FB0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2988" yWindow="2100" windowWidth="17280" windowHeight="8880" activeTab="1" xr2:uid="{E4BAE67D-7837-4FED-B4EB-774E74865D14}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E4BAE67D-7837-4FED-B4EB-774E74865D14}"/>
   </bookViews>
   <sheets>
     <sheet name="Registration" sheetId="1" r:id="rId1"/>
     <sheet name="Address" sheetId="2" r:id="rId2"/>
+    <sheet name="MultiAddressData" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="877" uniqueCount="265">
   <si>
     <t>Gender</t>
   </si>
@@ -49,18 +50,9 @@
     <t>Male</t>
   </si>
   <si>
-    <t>MK2316@</t>
-  </si>
-  <si>
     <t>Manoj Kiyan</t>
   </si>
   <si>
-    <t>M</t>
-  </si>
-  <si>
-    <t>mk2316@gmail.com</t>
-  </si>
-  <si>
     <t>Comapany</t>
   </si>
   <si>
@@ -104,6 +96,732 @@
   </si>
   <si>
     <t>TamilNadu</t>
+  </si>
+  <si>
+    <t>India</t>
+  </si>
+  <si>
+    <t>Anitha</t>
+  </si>
+  <si>
+    <t>Kumar</t>
+  </si>
+  <si>
+    <t>anitha.kumar402@gmail.com</t>
+  </si>
+  <si>
+    <t>CloudNest</t>
+  </si>
+  <si>
+    <t>Salem</t>
+  </si>
+  <si>
+    <t>No.644, Park Avenue</t>
+  </si>
+  <si>
+    <t>Karnataka</t>
+  </si>
+  <si>
+    <t>Rahul</t>
+  </si>
+  <si>
+    <t>Raj</t>
+  </si>
+  <si>
+    <t>rahul.raj576@gmail.com</t>
+  </si>
+  <si>
+    <t>TechNova</t>
+  </si>
+  <si>
+    <t>Hyderabad</t>
+  </si>
+  <si>
+    <t>No.950, North Street</t>
+  </si>
+  <si>
+    <t>Sneha</t>
+  </si>
+  <si>
+    <t>Prasad</t>
+  </si>
+  <si>
+    <t>sneha.prasad887@gmail.com</t>
+  </si>
+  <si>
+    <t>NextGen</t>
+  </si>
+  <si>
+    <t>Erode</t>
+  </si>
+  <si>
+    <t>No.800, Lake View</t>
+  </si>
+  <si>
+    <t>Rohit</t>
+  </si>
+  <si>
+    <t>Kiyan</t>
+  </si>
+  <si>
+    <t>rohit.kiyan872@gmail.com</t>
+  </si>
+  <si>
+    <t>InnovaSoft</t>
+  </si>
+  <si>
+    <t>Mumbai</t>
+  </si>
+  <si>
+    <t>No.413, Park Avenue</t>
+  </si>
+  <si>
+    <t>Maharashtra</t>
+  </si>
+  <si>
+    <t>Joseph</t>
+  </si>
+  <si>
+    <t>rohit.joseph558@gmail.com</t>
+  </si>
+  <si>
+    <t>VisionTech</t>
+  </si>
+  <si>
+    <t>No.875, Lake View</t>
+  </si>
+  <si>
+    <t>Vijay</t>
+  </si>
+  <si>
+    <t>Raman</t>
+  </si>
+  <si>
+    <t>vijay.raman856@gmail.com</t>
+  </si>
+  <si>
+    <t>No.850, North Street</t>
+  </si>
+  <si>
+    <t>Sharma</t>
+  </si>
+  <si>
+    <t>sneha.sharma215@gmail.com</t>
+  </si>
+  <si>
+    <t>Trichy</t>
+  </si>
+  <si>
+    <t>No.476, Park Avenue</t>
+  </si>
+  <si>
+    <t>Manoj</t>
+  </si>
+  <si>
+    <t>Gupta</t>
+  </si>
+  <si>
+    <t>manoj.gupta883@gmail.com</t>
+  </si>
+  <si>
+    <t>Madurai</t>
+  </si>
+  <si>
+    <t>No.292, Park Avenue</t>
+  </si>
+  <si>
+    <t>vijay.raman680@gmail.com</t>
+  </si>
+  <si>
+    <t>DataSpark</t>
+  </si>
+  <si>
+    <t>No.731, Gandhi Street</t>
+  </si>
+  <si>
+    <t>Divya</t>
+  </si>
+  <si>
+    <t>Verma</t>
+  </si>
+  <si>
+    <t>divya.verma579@gmail.com</t>
+  </si>
+  <si>
+    <t>CodeCraft</t>
+  </si>
+  <si>
+    <t>Coimbatore</t>
+  </si>
+  <si>
+    <t>No.385, Park Avenue</t>
+  </si>
+  <si>
+    <t>Mohan</t>
+  </si>
+  <si>
+    <t>anitha.mohan664@gmail.com</t>
+  </si>
+  <si>
+    <t>No.935, Nehru Nagar</t>
+  </si>
+  <si>
+    <t>Telangana</t>
+  </si>
+  <si>
+    <t>Kiran</t>
+  </si>
+  <si>
+    <t>Nair</t>
+  </si>
+  <si>
+    <t>kiran.nair413@gmail.com</t>
+  </si>
+  <si>
+    <t>Pune</t>
+  </si>
+  <si>
+    <t>No.554, Nehru Nagar</t>
+  </si>
+  <si>
+    <t>Ajay</t>
+  </si>
+  <si>
+    <t>ajay.joseph887@gmail.com</t>
+  </si>
+  <si>
+    <t>No.662, Anna Nagar</t>
+  </si>
+  <si>
+    <t>Deepak</t>
+  </si>
+  <si>
+    <t>Patel</t>
+  </si>
+  <si>
+    <t>deepak.patel318@gmail.com</t>
+  </si>
+  <si>
+    <t>FusionIT</t>
+  </si>
+  <si>
+    <t>No.792, Nehru Nagar</t>
+  </si>
+  <si>
+    <t>Arun</t>
+  </si>
+  <si>
+    <t>arun.patel613@gmail.com</t>
+  </si>
+  <si>
+    <t>No.993, Park Avenue</t>
+  </si>
+  <si>
+    <t>kiran.verma604@gmail.com</t>
+  </si>
+  <si>
+    <t>No.154, Temple Street</t>
+  </si>
+  <si>
+    <t>arun.prasad341@gmail.com</t>
+  </si>
+  <si>
+    <t>No.218, South Street</t>
+  </si>
+  <si>
+    <t>Suresh</t>
+  </si>
+  <si>
+    <t>Iyer</t>
+  </si>
+  <si>
+    <t>suresh.iyer779@gmail.com</t>
+  </si>
+  <si>
+    <t>No.973, MG Road</t>
+  </si>
+  <si>
+    <t>kiran.nair288@gmail.com</t>
+  </si>
+  <si>
+    <t>Bengaluru</t>
+  </si>
+  <si>
+    <t>No.979, North Street</t>
+  </si>
+  <si>
+    <t>Akash</t>
+  </si>
+  <si>
+    <t>akash.iyer143@gmail.com</t>
+  </si>
+  <si>
+    <t>No.593, Main Road</t>
+  </si>
+  <si>
+    <t>Das</t>
+  </si>
+  <si>
+    <t>manoj.das242@gmail.com</t>
+  </si>
+  <si>
+    <t>No.280, MG Road</t>
+  </si>
+  <si>
+    <t>Naveen</t>
+  </si>
+  <si>
+    <t>naveen.mathiyalagan487@gmail.com</t>
+  </si>
+  <si>
+    <t>No.720, South Street</t>
+  </si>
+  <si>
+    <t>deepak.iyer735@gmail.com</t>
+  </si>
+  <si>
+    <t>No.865, Park Avenue</t>
+  </si>
+  <si>
+    <t>Paul</t>
+  </si>
+  <si>
+    <t>naveen.paul277@gmail.com</t>
+  </si>
+  <si>
+    <t>No.292, North Street</t>
+  </si>
+  <si>
+    <t>Singh</t>
+  </si>
+  <si>
+    <t>arun.singh123@gmail.com</t>
+  </si>
+  <si>
+    <t>No.36, Park Avenue</t>
+  </si>
+  <si>
+    <t>divya.das909@gmail.com</t>
+  </si>
+  <si>
+    <t>No.926, Temple Street</t>
+  </si>
+  <si>
+    <t>Lavanya</t>
+  </si>
+  <si>
+    <t>lavanya.gupta81@gmail.com</t>
+  </si>
+  <si>
+    <t>PixelWorks</t>
+  </si>
+  <si>
+    <t>No.180, Main Road</t>
+  </si>
+  <si>
+    <t>Sanjay</t>
+  </si>
+  <si>
+    <t>sanjay.iyer369@gmail.com</t>
+  </si>
+  <si>
+    <t>No.276, Main Road</t>
+  </si>
+  <si>
+    <t>Priya</t>
+  </si>
+  <si>
+    <t>priya.mathiyalagan883@gmail.com</t>
+  </si>
+  <si>
+    <t>No.429, Park Avenue</t>
+  </si>
+  <si>
+    <t>Khan</t>
+  </si>
+  <si>
+    <t>deepak.khan990@gmail.com</t>
+  </si>
+  <si>
+    <t>No.880, Gandhi Street</t>
+  </si>
+  <si>
+    <t>rohit.patel944@gmail.com</t>
+  </si>
+  <si>
+    <t>No.891, Main Road</t>
+  </si>
+  <si>
+    <t>sanjay.khan2@gmail.com</t>
+  </si>
+  <si>
+    <t>No.386, Park Avenue</t>
+  </si>
+  <si>
+    <t>priya.verma438@gmail.com</t>
+  </si>
+  <si>
+    <t>No.275, Park Avenue</t>
+  </si>
+  <si>
+    <t>kiran.mohan300@gmail.com</t>
+  </si>
+  <si>
+    <t>No.467, MG Road</t>
+  </si>
+  <si>
+    <t>Karthik</t>
+  </si>
+  <si>
+    <t>karthik.das182@gmail.com</t>
+  </si>
+  <si>
+    <t>No.86, Nehru Nagar</t>
+  </si>
+  <si>
+    <t>Reddy</t>
+  </si>
+  <si>
+    <t>sanjay.reddy408@gmail.com</t>
+  </si>
+  <si>
+    <t>No.862, Main Road</t>
+  </si>
+  <si>
+    <t>suresh.joseph130@gmail.com</t>
+  </si>
+  <si>
+    <t>No.639, Main Road</t>
+  </si>
+  <si>
+    <t>priya.nair833@gmail.com</t>
+  </si>
+  <si>
+    <t>No.168, MG Road</t>
+  </si>
+  <si>
+    <t>manoj.sharma937@gmail.com</t>
+  </si>
+  <si>
+    <t>No.742, Gandhi Street</t>
+  </si>
+  <si>
+    <t>divya.singh878@gmail.com</t>
+  </si>
+  <si>
+    <t>No.373, MG Road</t>
+  </si>
+  <si>
+    <t>divya.raj653@gmail.com</t>
+  </si>
+  <si>
+    <t>No.76, Gandhi Street</t>
+  </si>
+  <si>
+    <t>rohit.raman299@gmail.com</t>
+  </si>
+  <si>
+    <t>No.348, Park Avenue</t>
+  </si>
+  <si>
+    <t>rahul.iyer446@gmail.com</t>
+  </si>
+  <si>
+    <t>No.193, Temple Street</t>
+  </si>
+  <si>
+    <t>anitha.reddy617@gmail.com</t>
+  </si>
+  <si>
+    <t>No.897, North Street</t>
+  </si>
+  <si>
+    <t>Harini</t>
+  </si>
+  <si>
+    <t>harini.kiyan699@gmail.com</t>
+  </si>
+  <si>
+    <t>No.954, Temple Street</t>
+  </si>
+  <si>
+    <t>manoj.nair766@gmail.com</t>
+  </si>
+  <si>
+    <t>No.764, Anna Nagar</t>
+  </si>
+  <si>
+    <t>divya.joseph595@gmail.com</t>
+  </si>
+  <si>
+    <t>No.602, Main Road</t>
+  </si>
+  <si>
+    <t>rahul.sharma227@gmail.com</t>
+  </si>
+  <si>
+    <t>No.558, Gandhi Street</t>
+  </si>
+  <si>
+    <t>suresh.mohan915@gmail.com</t>
+  </si>
+  <si>
+    <t>No.812, Main Road</t>
+  </si>
+  <si>
+    <t>harini.nair327@gmail.com</t>
+  </si>
+  <si>
+    <t>No.958, MG Road</t>
+  </si>
+  <si>
+    <t>vijay.paul280@gmail.com</t>
+  </si>
+  <si>
+    <t>No.364, Gandhi Street</t>
+  </si>
+  <si>
+    <t>karthik.paul101@gmail.com</t>
+  </si>
+  <si>
+    <t>No.614, South Street</t>
+  </si>
+  <si>
+    <t>kiran.patel63@gmail.com</t>
+  </si>
+  <si>
+    <t>No.691, Nehru Nagar</t>
+  </si>
+  <si>
+    <t>Babu</t>
+  </si>
+  <si>
+    <t>lavanya.babu759@gmail.com</t>
+  </si>
+  <si>
+    <t>No.928, Nehru Nagar</t>
+  </si>
+  <si>
+    <t>kiran.mohan129@gmail.com</t>
+  </si>
+  <si>
+    <t>No.254, South Street</t>
+  </si>
+  <si>
+    <t>arun.mohan827@gmail.com</t>
+  </si>
+  <si>
+    <t>No.921, North Street</t>
+  </si>
+  <si>
+    <t>divya.das347@gmail.com</t>
+  </si>
+  <si>
+    <t>No.921, Gandhi Street</t>
+  </si>
+  <si>
+    <t>sneha.kumar28@gmail.com</t>
+  </si>
+  <si>
+    <t>No.375, MG Road</t>
+  </si>
+  <si>
+    <t>anitha.raj520@gmail.com</t>
+  </si>
+  <si>
+    <t>No.925, Park Avenue</t>
+  </si>
+  <si>
+    <t>karthik.paul502@gmail.com</t>
+  </si>
+  <si>
+    <t>No.427, Anna Nagar</t>
+  </si>
+  <si>
+    <t>CountryName</t>
+  </si>
+  <si>
+    <t>Female</t>
+  </si>
+  <si>
+    <t>Anitha@223</t>
+  </si>
+  <si>
+    <t>Rahul@323</t>
+  </si>
+  <si>
+    <t>Sneha@423</t>
+  </si>
+  <si>
+    <t>Rohit@523</t>
+  </si>
+  <si>
+    <t>Rohit@623</t>
+  </si>
+  <si>
+    <t>Vijay@723</t>
+  </si>
+  <si>
+    <t>Sneha@823</t>
+  </si>
+  <si>
+    <t>Manoj@923</t>
+  </si>
+  <si>
+    <t>Vijay@1023</t>
+  </si>
+  <si>
+    <t>Divya@1123</t>
+  </si>
+  <si>
+    <t>Anitha@1223</t>
+  </si>
+  <si>
+    <t>Kiran@1323</t>
+  </si>
+  <si>
+    <t>Ajay@1423</t>
+  </si>
+  <si>
+    <t>Deepak@1523</t>
+  </si>
+  <si>
+    <t>Arun@1623</t>
+  </si>
+  <si>
+    <t>Kiran@1723</t>
+  </si>
+  <si>
+    <t>Arun@1823</t>
+  </si>
+  <si>
+    <t>Suresh@1923</t>
+  </si>
+  <si>
+    <t>Kiran@2023</t>
+  </si>
+  <si>
+    <t>Akash@2123</t>
+  </si>
+  <si>
+    <t>Manoj@2223</t>
+  </si>
+  <si>
+    <t>Naveen@2323</t>
+  </si>
+  <si>
+    <t>Deepak@2423</t>
+  </si>
+  <si>
+    <t>Naveen@2523</t>
+  </si>
+  <si>
+    <t>Arun@2623</t>
+  </si>
+  <si>
+    <t>Divya@2723</t>
+  </si>
+  <si>
+    <t>Lavanya@2823</t>
+  </si>
+  <si>
+    <t>Sanjay@2923</t>
+  </si>
+  <si>
+    <t>Priya@3023</t>
+  </si>
+  <si>
+    <t>Deepak@3123</t>
+  </si>
+  <si>
+    <t>Rohit@3223</t>
+  </si>
+  <si>
+    <t>Sanjay@3323</t>
+  </si>
+  <si>
+    <t>Priya@3423</t>
+  </si>
+  <si>
+    <t>Kiran@3523</t>
+  </si>
+  <si>
+    <t>Karthik@3623</t>
+  </si>
+  <si>
+    <t>Sanjay@3723</t>
+  </si>
+  <si>
+    <t>Suresh@3823</t>
+  </si>
+  <si>
+    <t>Priya@3923</t>
+  </si>
+  <si>
+    <t>Manoj@4023</t>
+  </si>
+  <si>
+    <t>Divya@4123</t>
+  </si>
+  <si>
+    <t>Divya@4223</t>
+  </si>
+  <si>
+    <t>Rohit@4323</t>
+  </si>
+  <si>
+    <t>Rahul@4423</t>
+  </si>
+  <si>
+    <t>Anitha@4523</t>
+  </si>
+  <si>
+    <t>Harini@4623</t>
+  </si>
+  <si>
+    <t>Manoj@4723</t>
+  </si>
+  <si>
+    <t>Divya@4823</t>
+  </si>
+  <si>
+    <t>Rahul@4923</t>
+  </si>
+  <si>
+    <t>Suresh@5023</t>
+  </si>
+  <si>
+    <t>Harini@5123</t>
+  </si>
+  <si>
+    <t>Vijay@5223</t>
+  </si>
+  <si>
+    <t>Karthik@5323</t>
+  </si>
+  <si>
+    <t>Kiran@5423</t>
+  </si>
+  <si>
+    <t>Lavanya@5523</t>
+  </si>
+  <si>
+    <t>Kiran@5623</t>
+  </si>
+  <si>
+    <t>Arun@5723</t>
+  </si>
+  <si>
+    <t>Divya@5823</t>
+  </si>
+  <si>
+    <t>Sneha@5923</t>
+  </si>
+  <si>
+    <t>Anitha@6023</t>
+  </si>
+  <si>
+    <t>Karthik@6123</t>
   </si>
 </sst>
 </file>
@@ -156,20 +874,24 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Hyperlink 2" xfId="2" xr:uid="{517DA6B8-9425-401F-B393-91A15245FE4A}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -482,13 +1204,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51171A60-04B5-4EBC-9205-5273F9D7C8B4}">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="15.6640625" customWidth="1"/>
     <col min="2" max="2" width="13.77734375" customWidth="1"/>
     <col min="3" max="3" width="19.109375" customWidth="1"/>
-    <col min="4" max="4" width="17.5546875" customWidth="1"/>
+    <col min="4" max="4" width="25.6640625" customWidth="1"/>
     <col min="5" max="5" width="17.88671875" customWidth="1"/>
     <col min="6" max="6" width="22.6640625" customWidth="1"/>
   </cols>
@@ -515,30 +1237,1205 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
+        <v>204</v>
+      </c>
+      <c r="B2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
         <v>6</v>
       </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>7</v>
+      <c r="B3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
+        <v>204</v>
+      </c>
+      <c r="B4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" t="s">
+        <v>204</v>
+      </c>
+      <c r="B5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D5" t="s">
+        <v>45</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" t="s">
+        <v>204</v>
+      </c>
+      <c r="B6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" t="s">
+        <v>50</v>
+      </c>
+      <c r="D6" t="s">
+        <v>51</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D7" t="s">
+        <v>56</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" t="s">
+        <v>204</v>
+      </c>
+      <c r="B8" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" t="s">
+        <v>58</v>
+      </c>
+      <c r="D8" t="s">
+        <v>59</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" t="s">
+        <v>62</v>
+      </c>
+      <c r="C9" t="s">
+        <v>63</v>
+      </c>
+      <c r="D9" t="s">
+        <v>64</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" t="s">
+        <v>54</v>
+      </c>
+      <c r="C10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D10" t="s">
+        <v>67</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" t="s">
+        <v>204</v>
+      </c>
+      <c r="B11" t="s">
+        <v>70</v>
+      </c>
+      <c r="C11" t="s">
+        <v>71</v>
+      </c>
+      <c r="D11" t="s">
+        <v>72</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" t="s">
+        <v>204</v>
+      </c>
+      <c r="B12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" t="s">
+        <v>76</v>
+      </c>
+      <c r="D12" t="s">
+        <v>77</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" t="s">
+        <v>6</v>
+      </c>
+      <c r="B13" t="s">
+        <v>80</v>
+      </c>
+      <c r="C13" t="s">
+        <v>81</v>
+      </c>
+      <c r="D13" t="s">
+        <v>82</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14" t="s">
+        <v>85</v>
+      </c>
+      <c r="C14" t="s">
+        <v>50</v>
+      </c>
+      <c r="D14" t="s">
+        <v>86</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" t="s">
+        <v>204</v>
+      </c>
+      <c r="B15" t="s">
+        <v>88</v>
+      </c>
+      <c r="C15" t="s">
+        <v>89</v>
+      </c>
+      <c r="D15" t="s">
+        <v>90</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" t="s">
+        <v>6</v>
+      </c>
+      <c r="B16" t="s">
+        <v>93</v>
+      </c>
+      <c r="C16" t="s">
+        <v>89</v>
+      </c>
+      <c r="D16" t="s">
+        <v>94</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" t="s">
+        <v>6</v>
+      </c>
+      <c r="B17" t="s">
+        <v>80</v>
+      </c>
+      <c r="C17" t="s">
+        <v>71</v>
+      </c>
+      <c r="D17" t="s">
+        <v>96</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" t="s">
+        <v>6</v>
+      </c>
+      <c r="B18" t="s">
+        <v>93</v>
+      </c>
+      <c r="C18" t="s">
+        <v>38</v>
+      </c>
+      <c r="D18" t="s">
+        <v>98</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" t="s">
+        <v>6</v>
+      </c>
+      <c r="B19" t="s">
+        <v>100</v>
+      </c>
+      <c r="C19" t="s">
+        <v>101</v>
+      </c>
+      <c r="D19" t="s">
+        <v>102</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" t="s">
+        <v>6</v>
+      </c>
+      <c r="B20" t="s">
+        <v>80</v>
+      </c>
+      <c r="C20" t="s">
+        <v>81</v>
+      </c>
+      <c r="D20" t="s">
+        <v>104</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" t="s">
+        <v>6</v>
+      </c>
+      <c r="B21" t="s">
+        <v>107</v>
+      </c>
+      <c r="C21" t="s">
+        <v>101</v>
+      </c>
+      <c r="D21" t="s">
+        <v>108</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" t="s">
+        <v>6</v>
+      </c>
+      <c r="B22" t="s">
+        <v>62</v>
+      </c>
+      <c r="C22" t="s">
+        <v>110</v>
+      </c>
+      <c r="D22" t="s">
+        <v>111</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" t="s">
+        <v>6</v>
+      </c>
+      <c r="B23" t="s">
+        <v>113</v>
+      </c>
+      <c r="C23" t="s">
+        <v>17</v>
+      </c>
+      <c r="D23" t="s">
+        <v>114</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" t="s">
+        <v>204</v>
+      </c>
+      <c r="B24" t="s">
+        <v>88</v>
+      </c>
+      <c r="C24" t="s">
+        <v>101</v>
+      </c>
+      <c r="D24" t="s">
+        <v>116</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" t="s">
+        <v>204</v>
+      </c>
+      <c r="B25" t="s">
+        <v>113</v>
+      </c>
+      <c r="C25" t="s">
+        <v>118</v>
+      </c>
+      <c r="D25" t="s">
+        <v>119</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" t="s">
+        <v>6</v>
+      </c>
+      <c r="B26" t="s">
+        <v>93</v>
+      </c>
+      <c r="C26" t="s">
+        <v>121</v>
+      </c>
+      <c r="D26" t="s">
+        <v>122</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27" t="s">
+        <v>204</v>
+      </c>
+      <c r="B27" t="s">
+        <v>70</v>
+      </c>
+      <c r="C27" t="s">
+        <v>110</v>
+      </c>
+      <c r="D27" t="s">
+        <v>124</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28" t="s">
+        <v>204</v>
+      </c>
+      <c r="B28" t="s">
+        <v>126</v>
+      </c>
+      <c r="C28" t="s">
+        <v>63</v>
+      </c>
+      <c r="D28" t="s">
+        <v>127</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29" t="s">
+        <v>6</v>
+      </c>
+      <c r="B29" t="s">
+        <v>130</v>
+      </c>
+      <c r="C29" t="s">
+        <v>101</v>
+      </c>
+      <c r="D29" t="s">
+        <v>131</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" t="s">
+        <v>204</v>
+      </c>
+      <c r="B30" t="s">
+        <v>133</v>
+      </c>
+      <c r="C30" t="s">
+        <v>17</v>
+      </c>
+      <c r="D30" t="s">
+        <v>134</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31" t="s">
+        <v>204</v>
+      </c>
+      <c r="B31" t="s">
+        <v>88</v>
+      </c>
+      <c r="C31" t="s">
+        <v>136</v>
+      </c>
+      <c r="D31" t="s">
+        <v>137</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32" t="s">
+        <v>204</v>
+      </c>
+      <c r="B32" t="s">
+        <v>43</v>
+      </c>
+      <c r="C32" t="s">
+        <v>89</v>
+      </c>
+      <c r="D32" t="s">
+        <v>139</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" t="s">
+        <v>204</v>
+      </c>
+      <c r="B33" t="s">
+        <v>130</v>
+      </c>
+      <c r="C33" t="s">
+        <v>136</v>
+      </c>
+      <c r="D33" t="s">
+        <v>141</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34" t="s">
+        <v>204</v>
+      </c>
+      <c r="B34" t="s">
+        <v>133</v>
+      </c>
+      <c r="C34" t="s">
+        <v>71</v>
+      </c>
+      <c r="D34" t="s">
+        <v>143</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35" t="s">
+        <v>6</v>
+      </c>
+      <c r="B35" t="s">
+        <v>80</v>
+      </c>
+      <c r="C35" t="s">
+        <v>76</v>
+      </c>
+      <c r="D35" t="s">
+        <v>145</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36" t="s">
+        <v>6</v>
+      </c>
+      <c r="B36" t="s">
+        <v>147</v>
+      </c>
+      <c r="C36" t="s">
+        <v>110</v>
+      </c>
+      <c r="D36" t="s">
+        <v>148</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37" t="s">
+        <v>6</v>
+      </c>
+      <c r="B37" t="s">
+        <v>130</v>
+      </c>
+      <c r="C37" t="s">
+        <v>150</v>
+      </c>
+      <c r="D37" t="s">
+        <v>151</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38" t="s">
+        <v>6</v>
+      </c>
+      <c r="B38" t="s">
+        <v>100</v>
+      </c>
+      <c r="C38" t="s">
+        <v>50</v>
+      </c>
+      <c r="D38" t="s">
+        <v>153</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39" t="s">
+        <v>204</v>
+      </c>
+      <c r="B39" t="s">
+        <v>133</v>
+      </c>
+      <c r="C39" t="s">
+        <v>81</v>
+      </c>
+      <c r="D39" t="s">
+        <v>155</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40" t="s">
+        <v>6</v>
+      </c>
+      <c r="B40" t="s">
+        <v>62</v>
+      </c>
+      <c r="C40" t="s">
+        <v>58</v>
+      </c>
+      <c r="D40" t="s">
+        <v>157</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="A41" t="s">
+        <v>204</v>
+      </c>
+      <c r="B41" t="s">
+        <v>70</v>
+      </c>
+      <c r="C41" t="s">
+        <v>121</v>
+      </c>
+      <c r="D41" t="s">
+        <v>159</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="A42" t="s">
+        <v>204</v>
+      </c>
+      <c r="B42" t="s">
+        <v>70</v>
+      </c>
+      <c r="C42" t="s">
+        <v>32</v>
+      </c>
+      <c r="D42" t="s">
+        <v>161</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
+      <c r="A43" t="s">
+        <v>6</v>
+      </c>
+      <c r="B43" t="s">
+        <v>43</v>
+      </c>
+      <c r="C43" t="s">
+        <v>55</v>
+      </c>
+      <c r="D43" t="s">
+        <v>163</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="A44" t="s">
+        <v>6</v>
+      </c>
+      <c r="B44" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" t="s">
+        <v>101</v>
+      </c>
+      <c r="D44" t="s">
+        <v>165</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
+      <c r="A45" t="s">
+        <v>204</v>
+      </c>
+      <c r="B45" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" t="s">
+        <v>150</v>
+      </c>
+      <c r="D45" t="s">
+        <v>167</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6">
+      <c r="A46" t="s">
+        <v>204</v>
+      </c>
+      <c r="B46" t="s">
+        <v>169</v>
+      </c>
+      <c r="C46" t="s">
+        <v>44</v>
+      </c>
+      <c r="D46" t="s">
+        <v>170</v>
+      </c>
+      <c r="E46" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
+      <c r="A47" t="s">
+        <v>6</v>
+      </c>
+      <c r="B47" t="s">
+        <v>62</v>
+      </c>
+      <c r="C47" t="s">
+        <v>81</v>
+      </c>
+      <c r="D47" t="s">
+        <v>172</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="A48" t="s">
+        <v>204</v>
+      </c>
+      <c r="B48" t="s">
+        <v>70</v>
+      </c>
+      <c r="C48" t="s">
+        <v>50</v>
+      </c>
+      <c r="D48" t="s">
+        <v>174</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6">
+      <c r="A49" t="s">
+        <v>6</v>
+      </c>
+      <c r="B49" t="s">
+        <v>31</v>
+      </c>
+      <c r="C49" t="s">
+        <v>58</v>
+      </c>
+      <c r="D49" t="s">
+        <v>176</v>
+      </c>
+      <c r="E49" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6">
+      <c r="A50" t="s">
+        <v>6</v>
+      </c>
+      <c r="B50" t="s">
+        <v>100</v>
+      </c>
+      <c r="C50" t="s">
+        <v>76</v>
+      </c>
+      <c r="D50" t="s">
+        <v>178</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6">
+      <c r="A51" t="s">
+        <v>204</v>
+      </c>
+      <c r="B51" t="s">
+        <v>169</v>
+      </c>
+      <c r="C51" t="s">
+        <v>81</v>
+      </c>
+      <c r="D51" t="s">
+        <v>180</v>
+      </c>
+      <c r="E51" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6">
+      <c r="A52" t="s">
+        <v>6</v>
+      </c>
+      <c r="B52" t="s">
+        <v>54</v>
+      </c>
+      <c r="C52" t="s">
+        <v>118</v>
+      </c>
+      <c r="D52" t="s">
+        <v>182</v>
+      </c>
+      <c r="E52" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6">
+      <c r="A53" t="s">
+        <v>6</v>
+      </c>
+      <c r="B53" t="s">
+        <v>147</v>
+      </c>
+      <c r="C53" t="s">
+        <v>118</v>
+      </c>
+      <c r="D53" t="s">
+        <v>184</v>
+      </c>
+      <c r="E53" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6">
+      <c r="A54" t="s">
+        <v>204</v>
+      </c>
+      <c r="B54" t="s">
+        <v>80</v>
+      </c>
+      <c r="C54" t="s">
+        <v>89</v>
+      </c>
+      <c r="D54" t="s">
+        <v>186</v>
+      </c>
+      <c r="E54" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="F54" s="4" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6">
+      <c r="A55" t="s">
+        <v>204</v>
+      </c>
+      <c r="B55" t="s">
+        <v>126</v>
+      </c>
+      <c r="C55" t="s">
+        <v>188</v>
+      </c>
+      <c r="D55" t="s">
+        <v>189</v>
+      </c>
+      <c r="E55" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="F55" s="4" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6">
+      <c r="A56" t="s">
+        <v>204</v>
+      </c>
+      <c r="B56" t="s">
+        <v>80</v>
+      </c>
+      <c r="C56" t="s">
+        <v>76</v>
+      </c>
+      <c r="D56" t="s">
+        <v>191</v>
+      </c>
+      <c r="E56" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="F56" s="4" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6">
+      <c r="A57" t="s">
+        <v>6</v>
+      </c>
+      <c r="B57" t="s">
+        <v>93</v>
+      </c>
+      <c r="C57" t="s">
+        <v>76</v>
+      </c>
+      <c r="D57" t="s">
+        <v>193</v>
+      </c>
+      <c r="E57" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="F57" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6">
+      <c r="A58" t="s">
+        <v>204</v>
+      </c>
+      <c r="B58" t="s">
+        <v>70</v>
+      </c>
+      <c r="C58" t="s">
+        <v>110</v>
+      </c>
+      <c r="D58" t="s">
+        <v>195</v>
+      </c>
+      <c r="E58" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="F58" s="4" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6">
+      <c r="A59" t="s">
+        <v>204</v>
+      </c>
+      <c r="B59" t="s">
+        <v>37</v>
+      </c>
+      <c r="C59" t="s">
+        <v>25</v>
+      </c>
+      <c r="D59" t="s">
+        <v>197</v>
+      </c>
+      <c r="E59" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="F59" s="4" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6">
+      <c r="A60" t="s">
+        <v>204</v>
+      </c>
+      <c r="B60" t="s">
+        <v>24</v>
+      </c>
+      <c r="C60" t="s">
+        <v>32</v>
+      </c>
+      <c r="D60" t="s">
+        <v>199</v>
+      </c>
+      <c r="E60" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="F60" s="4" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6">
+      <c r="A61" t="s">
+        <v>6</v>
+      </c>
+      <c r="B61" t="s">
+        <v>147</v>
+      </c>
+      <c r="C61" t="s">
+        <v>118</v>
+      </c>
+      <c r="D61" t="s">
+        <v>201</v>
+      </c>
+      <c r="E61" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="F61" s="4" t="s">
+        <v>264</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1" xr:uid="{079725A0-654B-45B9-800E-CDB18DD0F2A3}"/>
-    <hyperlink ref="E2" r:id="rId2" xr:uid="{E0AB63F2-B456-4EB0-8361-2D482707FA70}"/>
-    <hyperlink ref="F2" r:id="rId3" xr:uid="{7FEC9304-F679-4F3E-BA09-F91B2B3FEB7B}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -549,7 +2446,15 @@
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="20.21875" customWidth="1"/>
-    <col min="2" max="2" width="15.109375" customWidth="1"/>
+    <col min="2" max="2" width="21.5546875" customWidth="1"/>
+    <col min="3" max="3" width="25.77734375" customWidth="1"/>
+    <col min="4" max="4" width="17" customWidth="1"/>
+    <col min="5" max="5" width="16.109375" customWidth="1"/>
+    <col min="6" max="6" width="22.5546875" customWidth="1"/>
+    <col min="7" max="7" width="12.21875" customWidth="1"/>
+    <col min="8" max="8" width="13.21875" customWidth="1"/>
+    <col min="9" max="9" width="12.109375" customWidth="1"/>
+    <col min="10" max="10" width="11.44140625" customWidth="1"/>
     <col min="11" max="11" width="21.109375" customWidth="1"/>
     <col min="12" max="12" width="15.21875" customWidth="1"/>
   </cols>
@@ -565,60 +2470,60 @@
         <v>3</v>
       </c>
       <c r="D1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E1" t="s">
+      <c r="H1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F1" t="s">
+      <c r="I1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>16</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2">
-        <v>91</v>
+        <v>19</v>
+      </c>
+      <c r="E2" t="s">
+        <v>23</v>
       </c>
       <c r="F2">
         <v>49</v>
       </c>
       <c r="G2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J2">
         <v>614623</v>
@@ -636,4 +2541,2154 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7ECDF21-5BAF-4F1E-93A5-5291BBCA85D5}">
+  <dimension ref="A1:K61"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="25.33203125" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" t="s">
+        <v>203</v>
+      </c>
+      <c r="F1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I2">
+        <v>663246</v>
+      </c>
+      <c r="J2">
+        <v>9800355078</v>
+      </c>
+      <c r="K2">
+        <v>66135955</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G3" t="s">
+        <v>36</v>
+      </c>
+      <c r="H3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3">
+        <v>652307</v>
+      </c>
+      <c r="J3">
+        <v>9104072752</v>
+      </c>
+      <c r="K3">
+        <v>72205924</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" t="s">
+        <v>41</v>
+      </c>
+      <c r="G4" t="s">
+        <v>42</v>
+      </c>
+      <c r="H4" t="s">
+        <v>30</v>
+      </c>
+      <c r="I4">
+        <v>669037</v>
+      </c>
+      <c r="J4">
+        <v>9788156881</v>
+      </c>
+      <c r="K4">
+        <v>13102160</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D5" t="s">
+        <v>46</v>
+      </c>
+      <c r="E5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" t="s">
+        <v>47</v>
+      </c>
+      <c r="G5" t="s">
+        <v>48</v>
+      </c>
+      <c r="H5" t="s">
+        <v>49</v>
+      </c>
+      <c r="I5">
+        <v>619022</v>
+      </c>
+      <c r="J5">
+        <v>9504545607</v>
+      </c>
+      <c r="K5">
+        <v>65323703</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6" t="s">
+        <v>51</v>
+      </c>
+      <c r="D6" t="s">
+        <v>52</v>
+      </c>
+      <c r="E6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G6" t="s">
+        <v>53</v>
+      </c>
+      <c r="H6" t="s">
+        <v>49</v>
+      </c>
+      <c r="I6">
+        <v>651497</v>
+      </c>
+      <c r="J6">
+        <v>9360671644</v>
+      </c>
+      <c r="K6">
+        <v>75429178</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" t="s">
+        <v>54</v>
+      </c>
+      <c r="B7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C7" t="s">
+        <v>56</v>
+      </c>
+      <c r="D7" t="s">
+        <v>46</v>
+      </c>
+      <c r="E7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" t="s">
+        <v>28</v>
+      </c>
+      <c r="G7" t="s">
+        <v>57</v>
+      </c>
+      <c r="H7" t="s">
+        <v>30</v>
+      </c>
+      <c r="I7">
+        <v>622837</v>
+      </c>
+      <c r="J7">
+        <v>9068751640</v>
+      </c>
+      <c r="K7">
+        <v>18369703</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C8" t="s">
+        <v>59</v>
+      </c>
+      <c r="D8" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8" t="s">
+        <v>60</v>
+      </c>
+      <c r="G8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H8" t="s">
+        <v>49</v>
+      </c>
+      <c r="I8">
+        <v>619506</v>
+      </c>
+      <c r="J8">
+        <v>9549067104</v>
+      </c>
+      <c r="K8">
+        <v>45122785</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" t="s">
+        <v>62</v>
+      </c>
+      <c r="B9" t="s">
+        <v>63</v>
+      </c>
+      <c r="C9" t="s">
+        <v>64</v>
+      </c>
+      <c r="D9" t="s">
+        <v>27</v>
+      </c>
+      <c r="E9" t="s">
+        <v>23</v>
+      </c>
+      <c r="F9" t="s">
+        <v>65</v>
+      </c>
+      <c r="G9" t="s">
+        <v>66</v>
+      </c>
+      <c r="H9" t="s">
+        <v>49</v>
+      </c>
+      <c r="I9">
+        <v>658558</v>
+      </c>
+      <c r="J9">
+        <v>9003234176</v>
+      </c>
+      <c r="K9">
+        <v>91894236</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" t="s">
+        <v>54</v>
+      </c>
+      <c r="B10" t="s">
+        <v>55</v>
+      </c>
+      <c r="C10" t="s">
+        <v>67</v>
+      </c>
+      <c r="D10" t="s">
+        <v>68</v>
+      </c>
+      <c r="E10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F10" t="s">
+        <v>60</v>
+      </c>
+      <c r="G10" t="s">
+        <v>69</v>
+      </c>
+      <c r="H10" t="s">
+        <v>49</v>
+      </c>
+      <c r="I10">
+        <v>630822</v>
+      </c>
+      <c r="J10">
+        <v>9610234510</v>
+      </c>
+      <c r="K10">
+        <v>76735294</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" t="s">
+        <v>70</v>
+      </c>
+      <c r="B11" t="s">
+        <v>71</v>
+      </c>
+      <c r="C11" t="s">
+        <v>72</v>
+      </c>
+      <c r="D11" t="s">
+        <v>73</v>
+      </c>
+      <c r="E11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F11" t="s">
+        <v>74</v>
+      </c>
+      <c r="G11" t="s">
+        <v>75</v>
+      </c>
+      <c r="H11" t="s">
+        <v>49</v>
+      </c>
+      <c r="I11">
+        <v>650481</v>
+      </c>
+      <c r="J11">
+        <v>9633873480</v>
+      </c>
+      <c r="K11">
+        <v>46292922</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" t="s">
+        <v>76</v>
+      </c>
+      <c r="C12" t="s">
+        <v>77</v>
+      </c>
+      <c r="D12" t="s">
+        <v>46</v>
+      </c>
+      <c r="E12" t="s">
+        <v>23</v>
+      </c>
+      <c r="F12" t="s">
+        <v>65</v>
+      </c>
+      <c r="G12" t="s">
+        <v>78</v>
+      </c>
+      <c r="H12" t="s">
+        <v>79</v>
+      </c>
+      <c r="I12">
+        <v>669859</v>
+      </c>
+      <c r="J12">
+        <v>9179956992</v>
+      </c>
+      <c r="K12">
+        <v>83379885</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" t="s">
+        <v>80</v>
+      </c>
+      <c r="B13" t="s">
+        <v>81</v>
+      </c>
+      <c r="C13" t="s">
+        <v>82</v>
+      </c>
+      <c r="D13" t="s">
+        <v>40</v>
+      </c>
+      <c r="E13" t="s">
+        <v>23</v>
+      </c>
+      <c r="F13" t="s">
+        <v>83</v>
+      </c>
+      <c r="G13" t="s">
+        <v>84</v>
+      </c>
+      <c r="H13" t="s">
+        <v>30</v>
+      </c>
+      <c r="I13">
+        <v>621989</v>
+      </c>
+      <c r="J13">
+        <v>9703153227</v>
+      </c>
+      <c r="K13">
+        <v>17908744</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" t="s">
+        <v>85</v>
+      </c>
+      <c r="B14" t="s">
+        <v>50</v>
+      </c>
+      <c r="C14" t="s">
+        <v>86</v>
+      </c>
+      <c r="D14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E14" t="s">
+        <v>23</v>
+      </c>
+      <c r="F14" t="s">
+        <v>65</v>
+      </c>
+      <c r="G14" t="s">
+        <v>87</v>
+      </c>
+      <c r="H14" t="s">
+        <v>49</v>
+      </c>
+      <c r="I14">
+        <v>655856</v>
+      </c>
+      <c r="J14">
+        <v>9933795642</v>
+      </c>
+      <c r="K14">
+        <v>65679558</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" t="s">
+        <v>88</v>
+      </c>
+      <c r="B15" t="s">
+        <v>89</v>
+      </c>
+      <c r="C15" t="s">
+        <v>90</v>
+      </c>
+      <c r="D15" t="s">
+        <v>91</v>
+      </c>
+      <c r="E15" t="s">
+        <v>23</v>
+      </c>
+      <c r="F15" t="s">
+        <v>83</v>
+      </c>
+      <c r="G15" t="s">
+        <v>92</v>
+      </c>
+      <c r="H15" t="s">
+        <v>79</v>
+      </c>
+      <c r="I15">
+        <v>684144</v>
+      </c>
+      <c r="J15">
+        <v>9715118307</v>
+      </c>
+      <c r="K15">
+        <v>84156745</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" t="s">
+        <v>93</v>
+      </c>
+      <c r="B16" t="s">
+        <v>89</v>
+      </c>
+      <c r="C16" t="s">
+        <v>94</v>
+      </c>
+      <c r="D16" t="s">
+        <v>27</v>
+      </c>
+      <c r="E16" t="s">
+        <v>23</v>
+      </c>
+      <c r="F16" t="s">
+        <v>83</v>
+      </c>
+      <c r="G16" t="s">
+        <v>95</v>
+      </c>
+      <c r="H16" t="s">
+        <v>79</v>
+      </c>
+      <c r="I16">
+        <v>691479</v>
+      </c>
+      <c r="J16">
+        <v>9421390580</v>
+      </c>
+      <c r="K16">
+        <v>71864179</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" t="s">
+        <v>80</v>
+      </c>
+      <c r="B17" t="s">
+        <v>71</v>
+      </c>
+      <c r="C17" t="s">
+        <v>96</v>
+      </c>
+      <c r="D17" t="s">
+        <v>68</v>
+      </c>
+      <c r="E17" t="s">
+        <v>23</v>
+      </c>
+      <c r="F17" t="s">
+        <v>47</v>
+      </c>
+      <c r="G17" t="s">
+        <v>97</v>
+      </c>
+      <c r="H17" t="s">
+        <v>22</v>
+      </c>
+      <c r="I17">
+        <v>651374</v>
+      </c>
+      <c r="J17">
+        <v>9876479601</v>
+      </c>
+      <c r="K17">
+        <v>65444270</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" t="s">
+        <v>93</v>
+      </c>
+      <c r="B18" t="s">
+        <v>38</v>
+      </c>
+      <c r="C18" t="s">
+        <v>98</v>
+      </c>
+      <c r="D18" t="s">
+        <v>46</v>
+      </c>
+      <c r="E18" t="s">
+        <v>23</v>
+      </c>
+      <c r="F18" t="s">
+        <v>83</v>
+      </c>
+      <c r="G18" t="s">
+        <v>99</v>
+      </c>
+      <c r="H18" t="s">
+        <v>49</v>
+      </c>
+      <c r="I18">
+        <v>614728</v>
+      </c>
+      <c r="J18">
+        <v>9283978828</v>
+      </c>
+      <c r="K18">
+        <v>19804383</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" t="s">
+        <v>100</v>
+      </c>
+      <c r="B19" t="s">
+        <v>101</v>
+      </c>
+      <c r="C19" t="s">
+        <v>102</v>
+      </c>
+      <c r="D19" t="s">
+        <v>91</v>
+      </c>
+      <c r="E19" t="s">
+        <v>23</v>
+      </c>
+      <c r="F19" t="s">
+        <v>65</v>
+      </c>
+      <c r="G19" t="s">
+        <v>103</v>
+      </c>
+      <c r="H19" t="s">
+        <v>30</v>
+      </c>
+      <c r="I19">
+        <v>656124</v>
+      </c>
+      <c r="J19">
+        <v>9460803149</v>
+      </c>
+      <c r="K19">
+        <v>70170306</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" t="s">
+        <v>80</v>
+      </c>
+      <c r="B20" t="s">
+        <v>81</v>
+      </c>
+      <c r="C20" t="s">
+        <v>104</v>
+      </c>
+      <c r="D20" t="s">
+        <v>40</v>
+      </c>
+      <c r="E20" t="s">
+        <v>23</v>
+      </c>
+      <c r="F20" t="s">
+        <v>105</v>
+      </c>
+      <c r="G20" t="s">
+        <v>106</v>
+      </c>
+      <c r="H20" t="s">
+        <v>22</v>
+      </c>
+      <c r="I20">
+        <v>683483</v>
+      </c>
+      <c r="J20">
+        <v>9764535151</v>
+      </c>
+      <c r="K20">
+        <v>28276928</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" t="s">
+        <v>107</v>
+      </c>
+      <c r="B21" t="s">
+        <v>101</v>
+      </c>
+      <c r="C21" t="s">
+        <v>108</v>
+      </c>
+      <c r="D21" t="s">
+        <v>52</v>
+      </c>
+      <c r="E21" t="s">
+        <v>23</v>
+      </c>
+      <c r="F21" t="s">
+        <v>47</v>
+      </c>
+      <c r="G21" t="s">
+        <v>109</v>
+      </c>
+      <c r="H21" t="s">
+        <v>49</v>
+      </c>
+      <c r="I21">
+        <v>627601</v>
+      </c>
+      <c r="J21">
+        <v>9199364722</v>
+      </c>
+      <c r="K21">
+        <v>93092342</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" t="s">
+        <v>62</v>
+      </c>
+      <c r="B22" t="s">
+        <v>110</v>
+      </c>
+      <c r="C22" t="s">
+        <v>111</v>
+      </c>
+      <c r="D22" t="s">
+        <v>19</v>
+      </c>
+      <c r="E22" t="s">
+        <v>23</v>
+      </c>
+      <c r="F22" t="s">
+        <v>28</v>
+      </c>
+      <c r="G22" t="s">
+        <v>112</v>
+      </c>
+      <c r="H22" t="s">
+        <v>79</v>
+      </c>
+      <c r="I22">
+        <v>627321</v>
+      </c>
+      <c r="J22">
+        <v>9444149245</v>
+      </c>
+      <c r="K22">
+        <v>14743795</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" t="s">
+        <v>113</v>
+      </c>
+      <c r="B23" t="s">
+        <v>17</v>
+      </c>
+      <c r="C23" t="s">
+        <v>114</v>
+      </c>
+      <c r="D23" t="s">
+        <v>40</v>
+      </c>
+      <c r="E23" t="s">
+        <v>23</v>
+      </c>
+      <c r="F23" t="s">
+        <v>35</v>
+      </c>
+      <c r="G23" t="s">
+        <v>115</v>
+      </c>
+      <c r="H23" t="s">
+        <v>30</v>
+      </c>
+      <c r="I23">
+        <v>663682</v>
+      </c>
+      <c r="J23">
+        <v>9654787345</v>
+      </c>
+      <c r="K23">
+        <v>79156008</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" t="s">
+        <v>88</v>
+      </c>
+      <c r="B24" t="s">
+        <v>101</v>
+      </c>
+      <c r="C24" t="s">
+        <v>116</v>
+      </c>
+      <c r="D24" t="s">
+        <v>52</v>
+      </c>
+      <c r="E24" t="s">
+        <v>23</v>
+      </c>
+      <c r="F24" t="s">
+        <v>41</v>
+      </c>
+      <c r="G24" t="s">
+        <v>117</v>
+      </c>
+      <c r="H24" t="s">
+        <v>22</v>
+      </c>
+      <c r="I24">
+        <v>604711</v>
+      </c>
+      <c r="J24">
+        <v>9153785737</v>
+      </c>
+      <c r="K24">
+        <v>58223864</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25" t="s">
+        <v>113</v>
+      </c>
+      <c r="B25" t="s">
+        <v>118</v>
+      </c>
+      <c r="C25" t="s">
+        <v>119</v>
+      </c>
+      <c r="D25" t="s">
+        <v>34</v>
+      </c>
+      <c r="E25" t="s">
+        <v>23</v>
+      </c>
+      <c r="F25" t="s">
+        <v>47</v>
+      </c>
+      <c r="G25" t="s">
+        <v>120</v>
+      </c>
+      <c r="H25" t="s">
+        <v>22</v>
+      </c>
+      <c r="I25">
+        <v>668990</v>
+      </c>
+      <c r="J25">
+        <v>9582223481</v>
+      </c>
+      <c r="K25">
+        <v>45220861</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" t="s">
+        <v>93</v>
+      </c>
+      <c r="B26" t="s">
+        <v>121</v>
+      </c>
+      <c r="C26" t="s">
+        <v>122</v>
+      </c>
+      <c r="D26" t="s">
+        <v>91</v>
+      </c>
+      <c r="E26" t="s">
+        <v>23</v>
+      </c>
+      <c r="F26" t="s">
+        <v>60</v>
+      </c>
+      <c r="G26" t="s">
+        <v>123</v>
+      </c>
+      <c r="H26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I26">
+        <v>671831</v>
+      </c>
+      <c r="J26">
+        <v>9320497231</v>
+      </c>
+      <c r="K26">
+        <v>91990783</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" t="s">
+        <v>70</v>
+      </c>
+      <c r="B27" t="s">
+        <v>110</v>
+      </c>
+      <c r="C27" t="s">
+        <v>124</v>
+      </c>
+      <c r="D27" t="s">
+        <v>40</v>
+      </c>
+      <c r="E27" t="s">
+        <v>23</v>
+      </c>
+      <c r="F27" t="s">
+        <v>20</v>
+      </c>
+      <c r="G27" t="s">
+        <v>125</v>
+      </c>
+      <c r="H27" t="s">
+        <v>30</v>
+      </c>
+      <c r="I27">
+        <v>694659</v>
+      </c>
+      <c r="J27">
+        <v>9086654775</v>
+      </c>
+      <c r="K27">
+        <v>65222268</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" t="s">
+        <v>126</v>
+      </c>
+      <c r="B28" t="s">
+        <v>63</v>
+      </c>
+      <c r="C28" t="s">
+        <v>127</v>
+      </c>
+      <c r="D28" t="s">
+        <v>128</v>
+      </c>
+      <c r="E28" t="s">
+        <v>23</v>
+      </c>
+      <c r="F28" t="s">
+        <v>28</v>
+      </c>
+      <c r="G28" t="s">
+        <v>129</v>
+      </c>
+      <c r="H28" t="s">
+        <v>49</v>
+      </c>
+      <c r="I28">
+        <v>679177</v>
+      </c>
+      <c r="J28">
+        <v>9063107820</v>
+      </c>
+      <c r="K28">
+        <v>94946819</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" t="s">
+        <v>130</v>
+      </c>
+      <c r="B29" t="s">
+        <v>101</v>
+      </c>
+      <c r="C29" t="s">
+        <v>131</v>
+      </c>
+      <c r="D29" t="s">
+        <v>52</v>
+      </c>
+      <c r="E29" t="s">
+        <v>23</v>
+      </c>
+      <c r="F29" t="s">
+        <v>74</v>
+      </c>
+      <c r="G29" t="s">
+        <v>132</v>
+      </c>
+      <c r="H29" t="s">
+        <v>49</v>
+      </c>
+      <c r="I29">
+        <v>633597</v>
+      </c>
+      <c r="J29">
+        <v>9359597004</v>
+      </c>
+      <c r="K29">
+        <v>48027870</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30" t="s">
+        <v>133</v>
+      </c>
+      <c r="B30" t="s">
+        <v>17</v>
+      </c>
+      <c r="C30" t="s">
+        <v>134</v>
+      </c>
+      <c r="D30" t="s">
+        <v>40</v>
+      </c>
+      <c r="E30" t="s">
+        <v>23</v>
+      </c>
+      <c r="F30" t="s">
+        <v>41</v>
+      </c>
+      <c r="G30" t="s">
+        <v>135</v>
+      </c>
+      <c r="H30" t="s">
+        <v>22</v>
+      </c>
+      <c r="I30">
+        <v>614538</v>
+      </c>
+      <c r="J30">
+        <v>9985365885</v>
+      </c>
+      <c r="K30">
+        <v>22848600</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="A31" t="s">
+        <v>88</v>
+      </c>
+      <c r="B31" t="s">
+        <v>136</v>
+      </c>
+      <c r="C31" t="s">
+        <v>137</v>
+      </c>
+      <c r="D31" t="s">
+        <v>34</v>
+      </c>
+      <c r="E31" t="s">
+        <v>23</v>
+      </c>
+      <c r="F31" t="s">
+        <v>105</v>
+      </c>
+      <c r="G31" t="s">
+        <v>138</v>
+      </c>
+      <c r="H31" t="s">
+        <v>79</v>
+      </c>
+      <c r="I31">
+        <v>657825</v>
+      </c>
+      <c r="J31">
+        <v>9372752482</v>
+      </c>
+      <c r="K31">
+        <v>99977448</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="A32" t="s">
+        <v>43</v>
+      </c>
+      <c r="B32" t="s">
+        <v>89</v>
+      </c>
+      <c r="C32" t="s">
+        <v>139</v>
+      </c>
+      <c r="D32" t="s">
+        <v>73</v>
+      </c>
+      <c r="E32" t="s">
+        <v>23</v>
+      </c>
+      <c r="F32" t="s">
+        <v>65</v>
+      </c>
+      <c r="G32" t="s">
+        <v>140</v>
+      </c>
+      <c r="H32" t="s">
+        <v>30</v>
+      </c>
+      <c r="I32">
+        <v>632247</v>
+      </c>
+      <c r="J32">
+        <v>9116580681</v>
+      </c>
+      <c r="K32">
+        <v>30852667</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11">
+      <c r="A33" t="s">
+        <v>130</v>
+      </c>
+      <c r="B33" t="s">
+        <v>136</v>
+      </c>
+      <c r="C33" t="s">
+        <v>141</v>
+      </c>
+      <c r="D33" t="s">
+        <v>27</v>
+      </c>
+      <c r="E33" t="s">
+        <v>23</v>
+      </c>
+      <c r="F33" t="s">
+        <v>83</v>
+      </c>
+      <c r="G33" t="s">
+        <v>142</v>
+      </c>
+      <c r="H33" t="s">
+        <v>79</v>
+      </c>
+      <c r="I33">
+        <v>651528</v>
+      </c>
+      <c r="J33">
+        <v>9133021171</v>
+      </c>
+      <c r="K33">
+        <v>91634548</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11">
+      <c r="A34" t="s">
+        <v>133</v>
+      </c>
+      <c r="B34" t="s">
+        <v>71</v>
+      </c>
+      <c r="C34" t="s">
+        <v>143</v>
+      </c>
+      <c r="D34" t="s">
+        <v>34</v>
+      </c>
+      <c r="E34" t="s">
+        <v>23</v>
+      </c>
+      <c r="F34" t="s">
+        <v>74</v>
+      </c>
+      <c r="G34" t="s">
+        <v>144</v>
+      </c>
+      <c r="H34" t="s">
+        <v>30</v>
+      </c>
+      <c r="I34">
+        <v>627757</v>
+      </c>
+      <c r="J34">
+        <v>9856968612</v>
+      </c>
+      <c r="K34">
+        <v>74273912</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11">
+      <c r="A35" t="s">
+        <v>80</v>
+      </c>
+      <c r="B35" t="s">
+        <v>76</v>
+      </c>
+      <c r="C35" t="s">
+        <v>145</v>
+      </c>
+      <c r="D35" t="s">
+        <v>46</v>
+      </c>
+      <c r="E35" t="s">
+        <v>23</v>
+      </c>
+      <c r="F35" t="s">
+        <v>20</v>
+      </c>
+      <c r="G35" t="s">
+        <v>146</v>
+      </c>
+      <c r="H35" t="s">
+        <v>49</v>
+      </c>
+      <c r="I35">
+        <v>663940</v>
+      </c>
+      <c r="J35">
+        <v>9292828551</v>
+      </c>
+      <c r="K35">
+        <v>31404916</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11">
+      <c r="A36" t="s">
+        <v>147</v>
+      </c>
+      <c r="B36" t="s">
+        <v>110</v>
+      </c>
+      <c r="C36" t="s">
+        <v>148</v>
+      </c>
+      <c r="D36" t="s">
+        <v>52</v>
+      </c>
+      <c r="E36" t="s">
+        <v>23</v>
+      </c>
+      <c r="F36" t="s">
+        <v>105</v>
+      </c>
+      <c r="G36" t="s">
+        <v>149</v>
+      </c>
+      <c r="H36" t="s">
+        <v>22</v>
+      </c>
+      <c r="I36">
+        <v>613620</v>
+      </c>
+      <c r="J36">
+        <v>9285696816</v>
+      </c>
+      <c r="K36">
+        <v>20455494</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11">
+      <c r="A37" t="s">
+        <v>130</v>
+      </c>
+      <c r="B37" t="s">
+        <v>150</v>
+      </c>
+      <c r="C37" t="s">
+        <v>151</v>
+      </c>
+      <c r="D37" t="s">
+        <v>34</v>
+      </c>
+      <c r="E37" t="s">
+        <v>23</v>
+      </c>
+      <c r="F37" t="s">
+        <v>74</v>
+      </c>
+      <c r="G37" t="s">
+        <v>152</v>
+      </c>
+      <c r="H37" t="s">
+        <v>22</v>
+      </c>
+      <c r="I37">
+        <v>685569</v>
+      </c>
+      <c r="J37">
+        <v>9638507149</v>
+      </c>
+      <c r="K37">
+        <v>61084297</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11">
+      <c r="A38" t="s">
+        <v>100</v>
+      </c>
+      <c r="B38" t="s">
+        <v>50</v>
+      </c>
+      <c r="C38" t="s">
+        <v>153</v>
+      </c>
+      <c r="D38" t="s">
+        <v>128</v>
+      </c>
+      <c r="E38" t="s">
+        <v>23</v>
+      </c>
+      <c r="F38" t="s">
+        <v>105</v>
+      </c>
+      <c r="G38" t="s">
+        <v>154</v>
+      </c>
+      <c r="H38" t="s">
+        <v>30</v>
+      </c>
+      <c r="I38">
+        <v>637213</v>
+      </c>
+      <c r="J38">
+        <v>9944851292</v>
+      </c>
+      <c r="K38">
+        <v>48382949</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11">
+      <c r="A39" t="s">
+        <v>133</v>
+      </c>
+      <c r="B39" t="s">
+        <v>81</v>
+      </c>
+      <c r="C39" t="s">
+        <v>155</v>
+      </c>
+      <c r="D39" t="s">
+        <v>91</v>
+      </c>
+      <c r="E39" t="s">
+        <v>23</v>
+      </c>
+      <c r="F39" t="s">
+        <v>105</v>
+      </c>
+      <c r="G39" t="s">
+        <v>156</v>
+      </c>
+      <c r="H39" t="s">
+        <v>79</v>
+      </c>
+      <c r="I39">
+        <v>693215</v>
+      </c>
+      <c r="J39">
+        <v>9958516844</v>
+      </c>
+      <c r="K39">
+        <v>81837937</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11">
+      <c r="A40" t="s">
+        <v>62</v>
+      </c>
+      <c r="B40" t="s">
+        <v>58</v>
+      </c>
+      <c r="C40" t="s">
+        <v>157</v>
+      </c>
+      <c r="D40" t="s">
+        <v>46</v>
+      </c>
+      <c r="E40" t="s">
+        <v>23</v>
+      </c>
+      <c r="F40" t="s">
+        <v>35</v>
+      </c>
+      <c r="G40" t="s">
+        <v>158</v>
+      </c>
+      <c r="H40" t="s">
+        <v>30</v>
+      </c>
+      <c r="I40">
+        <v>667914</v>
+      </c>
+      <c r="J40">
+        <v>9273664200</v>
+      </c>
+      <c r="K40">
+        <v>45905466</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11">
+      <c r="A41" t="s">
+        <v>70</v>
+      </c>
+      <c r="B41" t="s">
+        <v>121</v>
+      </c>
+      <c r="C41" t="s">
+        <v>159</v>
+      </c>
+      <c r="D41" t="s">
+        <v>19</v>
+      </c>
+      <c r="E41" t="s">
+        <v>23</v>
+      </c>
+      <c r="F41" t="s">
+        <v>83</v>
+      </c>
+      <c r="G41" t="s">
+        <v>160</v>
+      </c>
+      <c r="H41" t="s">
+        <v>79</v>
+      </c>
+      <c r="I41">
+        <v>637348</v>
+      </c>
+      <c r="J41">
+        <v>9692703472</v>
+      </c>
+      <c r="K41">
+        <v>12371966</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11">
+      <c r="A42" t="s">
+        <v>70</v>
+      </c>
+      <c r="B42" t="s">
+        <v>32</v>
+      </c>
+      <c r="C42" t="s">
+        <v>161</v>
+      </c>
+      <c r="D42" t="s">
+        <v>46</v>
+      </c>
+      <c r="E42" t="s">
+        <v>23</v>
+      </c>
+      <c r="F42" t="s">
+        <v>83</v>
+      </c>
+      <c r="G42" t="s">
+        <v>162</v>
+      </c>
+      <c r="H42" t="s">
+        <v>49</v>
+      </c>
+      <c r="I42">
+        <v>613544</v>
+      </c>
+      <c r="J42">
+        <v>9189817976</v>
+      </c>
+      <c r="K42">
+        <v>12204998</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11">
+      <c r="A43" t="s">
+        <v>43</v>
+      </c>
+      <c r="B43" t="s">
+        <v>55</v>
+      </c>
+      <c r="C43" t="s">
+        <v>163</v>
+      </c>
+      <c r="D43" t="s">
+        <v>34</v>
+      </c>
+      <c r="E43" t="s">
+        <v>23</v>
+      </c>
+      <c r="F43" t="s">
+        <v>65</v>
+      </c>
+      <c r="G43" t="s">
+        <v>164</v>
+      </c>
+      <c r="H43" t="s">
+        <v>22</v>
+      </c>
+      <c r="I43">
+        <v>692559</v>
+      </c>
+      <c r="J43">
+        <v>9963966366</v>
+      </c>
+      <c r="K43">
+        <v>80310844</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11">
+      <c r="A44" t="s">
+        <v>31</v>
+      </c>
+      <c r="B44" t="s">
+        <v>101</v>
+      </c>
+      <c r="C44" t="s">
+        <v>165</v>
+      </c>
+      <c r="D44" t="s">
+        <v>68</v>
+      </c>
+      <c r="E44" t="s">
+        <v>23</v>
+      </c>
+      <c r="F44" t="s">
+        <v>83</v>
+      </c>
+      <c r="G44" t="s">
+        <v>166</v>
+      </c>
+      <c r="H44" t="s">
+        <v>22</v>
+      </c>
+      <c r="I44">
+        <v>634705</v>
+      </c>
+      <c r="J44">
+        <v>9054726093</v>
+      </c>
+      <c r="K44">
+        <v>76844679</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11">
+      <c r="A45" t="s">
+        <v>24</v>
+      </c>
+      <c r="B45" t="s">
+        <v>150</v>
+      </c>
+      <c r="C45" t="s">
+        <v>167</v>
+      </c>
+      <c r="D45" t="s">
+        <v>19</v>
+      </c>
+      <c r="E45" t="s">
+        <v>23</v>
+      </c>
+      <c r="F45" t="s">
+        <v>20</v>
+      </c>
+      <c r="G45" t="s">
+        <v>168</v>
+      </c>
+      <c r="H45" t="s">
+        <v>22</v>
+      </c>
+      <c r="I45">
+        <v>665627</v>
+      </c>
+      <c r="J45">
+        <v>9852579307</v>
+      </c>
+      <c r="K45">
+        <v>11395744</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11">
+      <c r="A46" t="s">
+        <v>169</v>
+      </c>
+      <c r="B46" t="s">
+        <v>44</v>
+      </c>
+      <c r="C46" t="s">
+        <v>170</v>
+      </c>
+      <c r="D46" t="s">
+        <v>128</v>
+      </c>
+      <c r="E46" t="s">
+        <v>23</v>
+      </c>
+      <c r="F46" t="s">
+        <v>28</v>
+      </c>
+      <c r="G46" t="s">
+        <v>171</v>
+      </c>
+      <c r="H46" t="s">
+        <v>22</v>
+      </c>
+      <c r="I46">
+        <v>656895</v>
+      </c>
+      <c r="J46">
+        <v>9394661861</v>
+      </c>
+      <c r="K46">
+        <v>75244623</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11">
+      <c r="A47" t="s">
+        <v>62</v>
+      </c>
+      <c r="B47" t="s">
+        <v>81</v>
+      </c>
+      <c r="C47" t="s">
+        <v>172</v>
+      </c>
+      <c r="D47" t="s">
+        <v>19</v>
+      </c>
+      <c r="E47" t="s">
+        <v>23</v>
+      </c>
+      <c r="F47" t="s">
+        <v>105</v>
+      </c>
+      <c r="G47" t="s">
+        <v>173</v>
+      </c>
+      <c r="H47" t="s">
+        <v>79</v>
+      </c>
+      <c r="I47">
+        <v>659099</v>
+      </c>
+      <c r="J47">
+        <v>9364797286</v>
+      </c>
+      <c r="K47">
+        <v>77985239</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11">
+      <c r="A48" t="s">
+        <v>70</v>
+      </c>
+      <c r="B48" t="s">
+        <v>50</v>
+      </c>
+      <c r="C48" t="s">
+        <v>174</v>
+      </c>
+      <c r="D48" t="s">
+        <v>73</v>
+      </c>
+      <c r="E48" t="s">
+        <v>23</v>
+      </c>
+      <c r="F48" t="s">
+        <v>65</v>
+      </c>
+      <c r="G48" t="s">
+        <v>175</v>
+      </c>
+      <c r="H48" t="s">
+        <v>30</v>
+      </c>
+      <c r="I48">
+        <v>663175</v>
+      </c>
+      <c r="J48">
+        <v>9775086883</v>
+      </c>
+      <c r="K48">
+        <v>55389084</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11">
+      <c r="A49" t="s">
+        <v>31</v>
+      </c>
+      <c r="B49" t="s">
+        <v>58</v>
+      </c>
+      <c r="C49" t="s">
+        <v>176</v>
+      </c>
+      <c r="D49" t="s">
+        <v>46</v>
+      </c>
+      <c r="E49" t="s">
+        <v>23</v>
+      </c>
+      <c r="F49" t="s">
+        <v>35</v>
+      </c>
+      <c r="G49" t="s">
+        <v>177</v>
+      </c>
+      <c r="H49" t="s">
+        <v>49</v>
+      </c>
+      <c r="I49">
+        <v>681897</v>
+      </c>
+      <c r="J49">
+        <v>9645394812</v>
+      </c>
+      <c r="K49">
+        <v>11412736</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11">
+      <c r="A50" t="s">
+        <v>100</v>
+      </c>
+      <c r="B50" t="s">
+        <v>76</v>
+      </c>
+      <c r="C50" t="s">
+        <v>178</v>
+      </c>
+      <c r="D50" t="s">
+        <v>27</v>
+      </c>
+      <c r="E50" t="s">
+        <v>23</v>
+      </c>
+      <c r="F50" t="s">
+        <v>105</v>
+      </c>
+      <c r="G50" t="s">
+        <v>179</v>
+      </c>
+      <c r="H50" t="s">
+        <v>79</v>
+      </c>
+      <c r="I50">
+        <v>610894</v>
+      </c>
+      <c r="J50">
+        <v>9617077684</v>
+      </c>
+      <c r="K50">
+        <v>19006686</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11">
+      <c r="A51" t="s">
+        <v>169</v>
+      </c>
+      <c r="B51" t="s">
+        <v>81</v>
+      </c>
+      <c r="C51" t="s">
+        <v>180</v>
+      </c>
+      <c r="D51" t="s">
+        <v>52</v>
+      </c>
+      <c r="E51" t="s">
+        <v>23</v>
+      </c>
+      <c r="F51" t="s">
+        <v>20</v>
+      </c>
+      <c r="G51" t="s">
+        <v>181</v>
+      </c>
+      <c r="H51" t="s">
+        <v>79</v>
+      </c>
+      <c r="I51">
+        <v>669529</v>
+      </c>
+      <c r="J51">
+        <v>9956430757</v>
+      </c>
+      <c r="K51">
+        <v>48054430</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11">
+      <c r="A52" t="s">
+        <v>54</v>
+      </c>
+      <c r="B52" t="s">
+        <v>118</v>
+      </c>
+      <c r="C52" t="s">
+        <v>182</v>
+      </c>
+      <c r="D52" t="s">
+        <v>34</v>
+      </c>
+      <c r="E52" t="s">
+        <v>23</v>
+      </c>
+      <c r="F52" t="s">
+        <v>105</v>
+      </c>
+      <c r="G52" t="s">
+        <v>183</v>
+      </c>
+      <c r="H52" t="s">
+        <v>79</v>
+      </c>
+      <c r="I52">
+        <v>619342</v>
+      </c>
+      <c r="J52">
+        <v>9933563299</v>
+      </c>
+      <c r="K52">
+        <v>13593826</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11">
+      <c r="A53" t="s">
+        <v>147</v>
+      </c>
+      <c r="B53" t="s">
+        <v>118</v>
+      </c>
+      <c r="C53" t="s">
+        <v>184</v>
+      </c>
+      <c r="D53" t="s">
+        <v>91</v>
+      </c>
+      <c r="E53" t="s">
+        <v>23</v>
+      </c>
+      <c r="F53" t="s">
+        <v>105</v>
+      </c>
+      <c r="G53" t="s">
+        <v>185</v>
+      </c>
+      <c r="H53" t="s">
+        <v>79</v>
+      </c>
+      <c r="I53">
+        <v>632704</v>
+      </c>
+      <c r="J53">
+        <v>9615523308</v>
+      </c>
+      <c r="K53">
+        <v>79105171</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11">
+      <c r="A54" t="s">
+        <v>80</v>
+      </c>
+      <c r="B54" t="s">
+        <v>89</v>
+      </c>
+      <c r="C54" t="s">
+        <v>186</v>
+      </c>
+      <c r="D54" t="s">
+        <v>128</v>
+      </c>
+      <c r="E54" t="s">
+        <v>23</v>
+      </c>
+      <c r="F54" t="s">
+        <v>41</v>
+      </c>
+      <c r="G54" t="s">
+        <v>187</v>
+      </c>
+      <c r="H54" t="s">
+        <v>79</v>
+      </c>
+      <c r="I54">
+        <v>633220</v>
+      </c>
+      <c r="J54">
+        <v>9690875272</v>
+      </c>
+      <c r="K54">
+        <v>45195298</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11">
+      <c r="A55" t="s">
+        <v>126</v>
+      </c>
+      <c r="B55" t="s">
+        <v>188</v>
+      </c>
+      <c r="C55" t="s">
+        <v>189</v>
+      </c>
+      <c r="D55" t="s">
+        <v>46</v>
+      </c>
+      <c r="E55" t="s">
+        <v>23</v>
+      </c>
+      <c r="F55" t="s">
+        <v>105</v>
+      </c>
+      <c r="G55" t="s">
+        <v>190</v>
+      </c>
+      <c r="H55" t="s">
+        <v>79</v>
+      </c>
+      <c r="I55">
+        <v>654484</v>
+      </c>
+      <c r="J55">
+        <v>9090137156</v>
+      </c>
+      <c r="K55">
+        <v>26697707</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11">
+      <c r="A56" t="s">
+        <v>80</v>
+      </c>
+      <c r="B56" t="s">
+        <v>76</v>
+      </c>
+      <c r="C56" t="s">
+        <v>191</v>
+      </c>
+      <c r="D56" t="s">
+        <v>19</v>
+      </c>
+      <c r="E56" t="s">
+        <v>23</v>
+      </c>
+      <c r="F56" t="s">
+        <v>60</v>
+      </c>
+      <c r="G56" t="s">
+        <v>192</v>
+      </c>
+      <c r="H56" t="s">
+        <v>79</v>
+      </c>
+      <c r="I56">
+        <v>680138</v>
+      </c>
+      <c r="J56">
+        <v>9748186739</v>
+      </c>
+      <c r="K56">
+        <v>34931990</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11">
+      <c r="A57" t="s">
+        <v>93</v>
+      </c>
+      <c r="B57" t="s">
+        <v>76</v>
+      </c>
+      <c r="C57" t="s">
+        <v>193</v>
+      </c>
+      <c r="D57" t="s">
+        <v>91</v>
+      </c>
+      <c r="E57" t="s">
+        <v>23</v>
+      </c>
+      <c r="F57" t="s">
+        <v>74</v>
+      </c>
+      <c r="G57" t="s">
+        <v>194</v>
+      </c>
+      <c r="H57" t="s">
+        <v>49</v>
+      </c>
+      <c r="I57">
+        <v>615814</v>
+      </c>
+      <c r="J57">
+        <v>9184191344</v>
+      </c>
+      <c r="K57">
+        <v>41622387</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11">
+      <c r="A58" t="s">
+        <v>70</v>
+      </c>
+      <c r="B58" t="s">
+        <v>110</v>
+      </c>
+      <c r="C58" t="s">
+        <v>195</v>
+      </c>
+      <c r="D58" t="s">
+        <v>73</v>
+      </c>
+      <c r="E58" t="s">
+        <v>23</v>
+      </c>
+      <c r="F58" t="s">
+        <v>74</v>
+      </c>
+      <c r="G58" t="s">
+        <v>196</v>
+      </c>
+      <c r="H58" t="s">
+        <v>79</v>
+      </c>
+      <c r="I58">
+        <v>678729</v>
+      </c>
+      <c r="J58">
+        <v>9100986260</v>
+      </c>
+      <c r="K58">
+        <v>29620619</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11">
+      <c r="A59" t="s">
+        <v>37</v>
+      </c>
+      <c r="B59" t="s">
+        <v>25</v>
+      </c>
+      <c r="C59" t="s">
+        <v>197</v>
+      </c>
+      <c r="D59" t="s">
+        <v>46</v>
+      </c>
+      <c r="E59" t="s">
+        <v>23</v>
+      </c>
+      <c r="F59" t="s">
+        <v>28</v>
+      </c>
+      <c r="G59" t="s">
+        <v>198</v>
+      </c>
+      <c r="H59" t="s">
+        <v>22</v>
+      </c>
+      <c r="I59">
+        <v>698550</v>
+      </c>
+      <c r="J59">
+        <v>9753116766</v>
+      </c>
+      <c r="K59">
+        <v>93152118</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11">
+      <c r="A60" t="s">
+        <v>24</v>
+      </c>
+      <c r="B60" t="s">
+        <v>32</v>
+      </c>
+      <c r="C60" t="s">
+        <v>199</v>
+      </c>
+      <c r="D60" t="s">
+        <v>128</v>
+      </c>
+      <c r="E60" t="s">
+        <v>23</v>
+      </c>
+      <c r="F60" t="s">
+        <v>65</v>
+      </c>
+      <c r="G60" t="s">
+        <v>200</v>
+      </c>
+      <c r="H60" t="s">
+        <v>30</v>
+      </c>
+      <c r="I60">
+        <v>674157</v>
+      </c>
+      <c r="J60">
+        <v>9403490326</v>
+      </c>
+      <c r="K60">
+        <v>18397809</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11">
+      <c r="A61" t="s">
+        <v>147</v>
+      </c>
+      <c r="B61" t="s">
+        <v>118</v>
+      </c>
+      <c r="C61" t="s">
+        <v>201</v>
+      </c>
+      <c r="D61" t="s">
+        <v>46</v>
+      </c>
+      <c r="E61" t="s">
+        <v>23</v>
+      </c>
+      <c r="F61" t="s">
+        <v>60</v>
+      </c>
+      <c r="G61" t="s">
+        <v>202</v>
+      </c>
+      <c r="H61" t="s">
+        <v>49</v>
+      </c>
+      <c r="I61">
+        <v>634692</v>
+      </c>
+      <c r="J61">
+        <v>9773849786</v>
+      </c>
+      <c r="K61">
+        <v>75366048</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/src/test/resources/testScriptData.xlsx
+++ b/src/test/resources/testScriptData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Automation Testing\Selenium\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02B07A4D-DEB8-4B32-8503-BF328361FB0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94130F06-832A-47C0-9A03-29D01FB75CC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E4BAE67D-7837-4FED-B4EB-774E74865D14}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="877" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="877" uniqueCount="267">
   <si>
     <t>Gender</t>
   </si>
@@ -644,9 +644,6 @@
     <t>Female</t>
   </si>
   <si>
-    <t>Anitha@223</t>
-  </si>
-  <si>
     <t>Rahul@323</t>
   </si>
   <si>
@@ -822,6 +819,15 @@
   </si>
   <si>
     <t>Karthik@6123</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>mk2316@gmail.com</t>
+  </si>
+  <si>
+    <t>MK2316@</t>
   </si>
 </sst>
 </file>
@@ -879,15 +885,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1237,22 +1241,22 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>204</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>205</v>
+        <v>264</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -1268,11 +1272,11 @@
       <c r="D3" t="s">
         <v>33</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>206</v>
+      <c r="E3" t="s">
+        <v>205</v>
+      </c>
+      <c r="F3" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -1288,11 +1292,11 @@
       <c r="D4" t="s">
         <v>39</v>
       </c>
-      <c r="E4" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>207</v>
+      <c r="E4" t="s">
+        <v>206</v>
+      </c>
+      <c r="F4" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -1308,11 +1312,11 @@
       <c r="D5" t="s">
         <v>45</v>
       </c>
-      <c r="E5" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>208</v>
+      <c r="E5" t="s">
+        <v>207</v>
+      </c>
+      <c r="F5" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -1328,11 +1332,11 @@
       <c r="D6" t="s">
         <v>51</v>
       </c>
-      <c r="E6" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>209</v>
+      <c r="E6" t="s">
+        <v>208</v>
+      </c>
+      <c r="F6" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -1348,11 +1352,11 @@
       <c r="D7" t="s">
         <v>56</v>
       </c>
-      <c r="E7" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>210</v>
+      <c r="E7" t="s">
+        <v>209</v>
+      </c>
+      <c r="F7" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1368,11 +1372,11 @@
       <c r="D8" t="s">
         <v>59</v>
       </c>
-      <c r="E8" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>211</v>
+      <c r="E8" t="s">
+        <v>210</v>
+      </c>
+      <c r="F8" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1388,11 +1392,11 @@
       <c r="D9" t="s">
         <v>64</v>
       </c>
-      <c r="E9" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>212</v>
+      <c r="E9" t="s">
+        <v>211</v>
+      </c>
+      <c r="F9" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1408,11 +1412,11 @@
       <c r="D10" t="s">
         <v>67</v>
       </c>
-      <c r="E10" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>213</v>
+      <c r="E10" t="s">
+        <v>212</v>
+      </c>
+      <c r="F10" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1428,11 +1432,11 @@
       <c r="D11" t="s">
         <v>72</v>
       </c>
-      <c r="E11" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>214</v>
+      <c r="E11" t="s">
+        <v>213</v>
+      </c>
+      <c r="F11" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1448,11 +1452,11 @@
       <c r="D12" t="s">
         <v>77</v>
       </c>
-      <c r="E12" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>215</v>
+      <c r="E12" t="s">
+        <v>214</v>
+      </c>
+      <c r="F12" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1468,11 +1472,11 @@
       <c r="D13" t="s">
         <v>82</v>
       </c>
-      <c r="E13" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>216</v>
+      <c r="E13" t="s">
+        <v>215</v>
+      </c>
+      <c r="F13" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1488,11 +1492,11 @@
       <c r="D14" t="s">
         <v>86</v>
       </c>
-      <c r="E14" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>217</v>
+      <c r="E14" t="s">
+        <v>216</v>
+      </c>
+      <c r="F14" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1508,11 +1512,11 @@
       <c r="D15" t="s">
         <v>90</v>
       </c>
-      <c r="E15" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>218</v>
+      <c r="E15" t="s">
+        <v>217</v>
+      </c>
+      <c r="F15" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1528,11 +1532,11 @@
       <c r="D16" t="s">
         <v>94</v>
       </c>
-      <c r="E16" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>219</v>
+      <c r="E16" t="s">
+        <v>218</v>
+      </c>
+      <c r="F16" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -1548,11 +1552,11 @@
       <c r="D17" t="s">
         <v>96</v>
       </c>
-      <c r="E17" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>220</v>
+      <c r="E17" t="s">
+        <v>219</v>
+      </c>
+      <c r="F17" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -1568,11 +1572,11 @@
       <c r="D18" t="s">
         <v>98</v>
       </c>
-      <c r="E18" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>221</v>
+      <c r="E18" t="s">
+        <v>220</v>
+      </c>
+      <c r="F18" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -1588,11 +1592,11 @@
       <c r="D19" t="s">
         <v>102</v>
       </c>
-      <c r="E19" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>222</v>
+      <c r="E19" t="s">
+        <v>221</v>
+      </c>
+      <c r="F19" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -1608,11 +1612,11 @@
       <c r="D20" t="s">
         <v>104</v>
       </c>
-      <c r="E20" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>223</v>
+      <c r="E20" t="s">
+        <v>222</v>
+      </c>
+      <c r="F20" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -1628,11 +1632,11 @@
       <c r="D21" t="s">
         <v>108</v>
       </c>
-      <c r="E21" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>224</v>
+      <c r="E21" t="s">
+        <v>223</v>
+      </c>
+      <c r="F21" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -1648,11 +1652,11 @@
       <c r="D22" t="s">
         <v>111</v>
       </c>
-      <c r="E22" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>225</v>
+      <c r="E22" t="s">
+        <v>224</v>
+      </c>
+      <c r="F22" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -1668,11 +1672,11 @@
       <c r="D23" t="s">
         <v>114</v>
       </c>
-      <c r="E23" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>226</v>
+      <c r="E23" t="s">
+        <v>225</v>
+      </c>
+      <c r="F23" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -1688,11 +1692,11 @@
       <c r="D24" t="s">
         <v>116</v>
       </c>
-      <c r="E24" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>227</v>
+      <c r="E24" t="s">
+        <v>226</v>
+      </c>
+      <c r="F24" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -1708,11 +1712,11 @@
       <c r="D25" t="s">
         <v>119</v>
       </c>
-      <c r="E25" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>228</v>
+      <c r="E25" t="s">
+        <v>227</v>
+      </c>
+      <c r="F25" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -1728,11 +1732,11 @@
       <c r="D26" t="s">
         <v>122</v>
       </c>
-      <c r="E26" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>229</v>
+      <c r="E26" t="s">
+        <v>228</v>
+      </c>
+      <c r="F26" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -1748,11 +1752,11 @@
       <c r="D27" t="s">
         <v>124</v>
       </c>
-      <c r="E27" s="4" t="s">
-        <v>230</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>230</v>
+      <c r="E27" t="s">
+        <v>229</v>
+      </c>
+      <c r="F27" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -1768,11 +1772,11 @@
       <c r="D28" t="s">
         <v>127</v>
       </c>
-      <c r="E28" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>231</v>
+      <c r="E28" t="s">
+        <v>230</v>
+      </c>
+      <c r="F28" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -1788,11 +1792,11 @@
       <c r="D29" t="s">
         <v>131</v>
       </c>
-      <c r="E29" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>232</v>
+      <c r="E29" t="s">
+        <v>231</v>
+      </c>
+      <c r="F29" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -1808,11 +1812,11 @@
       <c r="D30" t="s">
         <v>134</v>
       </c>
-      <c r="E30" s="4" t="s">
-        <v>233</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>233</v>
+      <c r="E30" t="s">
+        <v>232</v>
+      </c>
+      <c r="F30" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -1828,11 +1832,11 @@
       <c r="D31" t="s">
         <v>137</v>
       </c>
-      <c r="E31" s="4" t="s">
-        <v>234</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>234</v>
+      <c r="E31" t="s">
+        <v>233</v>
+      </c>
+      <c r="F31" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -1848,11 +1852,11 @@
       <c r="D32" t="s">
         <v>139</v>
       </c>
-      <c r="E32" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>235</v>
+      <c r="E32" t="s">
+        <v>234</v>
+      </c>
+      <c r="F32" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -1868,11 +1872,11 @@
       <c r="D33" t="s">
         <v>141</v>
       </c>
-      <c r="E33" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="F33" s="4" t="s">
-        <v>236</v>
+      <c r="E33" t="s">
+        <v>235</v>
+      </c>
+      <c r="F33" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -1888,11 +1892,11 @@
       <c r="D34" t="s">
         <v>143</v>
       </c>
-      <c r="E34" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="F34" s="4" t="s">
-        <v>237</v>
+      <c r="E34" t="s">
+        <v>236</v>
+      </c>
+      <c r="F34" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -1908,11 +1912,11 @@
       <c r="D35" t="s">
         <v>145</v>
       </c>
-      <c r="E35" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="F35" s="4" t="s">
-        <v>238</v>
+      <c r="E35" t="s">
+        <v>237</v>
+      </c>
+      <c r="F35" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -1928,11 +1932,11 @@
       <c r="D36" t="s">
         <v>148</v>
       </c>
-      <c r="E36" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="F36" s="4" t="s">
-        <v>239</v>
+      <c r="E36" t="s">
+        <v>238</v>
+      </c>
+      <c r="F36" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -1948,11 +1952,11 @@
       <c r="D37" t="s">
         <v>151</v>
       </c>
-      <c r="E37" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="F37" s="4" t="s">
-        <v>240</v>
+      <c r="E37" t="s">
+        <v>239</v>
+      </c>
+      <c r="F37" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -1968,11 +1972,11 @@
       <c r="D38" t="s">
         <v>153</v>
       </c>
-      <c r="E38" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="F38" s="4" t="s">
-        <v>241</v>
+      <c r="E38" t="s">
+        <v>240</v>
+      </c>
+      <c r="F38" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -1988,11 +1992,11 @@
       <c r="D39" t="s">
         <v>155</v>
       </c>
-      <c r="E39" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="F39" s="4" t="s">
-        <v>242</v>
+      <c r="E39" t="s">
+        <v>241</v>
+      </c>
+      <c r="F39" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -2008,11 +2012,11 @@
       <c r="D40" t="s">
         <v>157</v>
       </c>
-      <c r="E40" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="F40" s="4" t="s">
-        <v>243</v>
+      <c r="E40" t="s">
+        <v>242</v>
+      </c>
+      <c r="F40" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -2028,11 +2032,11 @@
       <c r="D41" t="s">
         <v>159</v>
       </c>
-      <c r="E41" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="F41" s="4" t="s">
-        <v>244</v>
+      <c r="E41" t="s">
+        <v>243</v>
+      </c>
+      <c r="F41" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -2048,11 +2052,11 @@
       <c r="D42" t="s">
         <v>161</v>
       </c>
-      <c r="E42" s="4" t="s">
-        <v>245</v>
-      </c>
-      <c r="F42" s="4" t="s">
-        <v>245</v>
+      <c r="E42" t="s">
+        <v>244</v>
+      </c>
+      <c r="F42" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -2068,11 +2072,11 @@
       <c r="D43" t="s">
         <v>163</v>
       </c>
-      <c r="E43" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="F43" s="4" t="s">
-        <v>246</v>
+      <c r="E43" t="s">
+        <v>245</v>
+      </c>
+      <c r="F43" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -2088,11 +2092,11 @@
       <c r="D44" t="s">
         <v>165</v>
       </c>
-      <c r="E44" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="F44" s="4" t="s">
-        <v>247</v>
+      <c r="E44" t="s">
+        <v>246</v>
+      </c>
+      <c r="F44" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -2108,11 +2112,11 @@
       <c r="D45" t="s">
         <v>167</v>
       </c>
-      <c r="E45" s="4" t="s">
-        <v>248</v>
-      </c>
-      <c r="F45" s="4" t="s">
-        <v>248</v>
+      <c r="E45" t="s">
+        <v>247</v>
+      </c>
+      <c r="F45" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -2128,11 +2132,11 @@
       <c r="D46" t="s">
         <v>170</v>
       </c>
-      <c r="E46" s="4" t="s">
-        <v>249</v>
-      </c>
-      <c r="F46" s="4" t="s">
-        <v>249</v>
+      <c r="E46" t="s">
+        <v>248</v>
+      </c>
+      <c r="F46" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -2148,11 +2152,11 @@
       <c r="D47" t="s">
         <v>172</v>
       </c>
-      <c r="E47" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="F47" s="4" t="s">
-        <v>250</v>
+      <c r="E47" t="s">
+        <v>249</v>
+      </c>
+      <c r="F47" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -2168,11 +2172,11 @@
       <c r="D48" t="s">
         <v>174</v>
       </c>
-      <c r="E48" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="F48" s="4" t="s">
-        <v>251</v>
+      <c r="E48" t="s">
+        <v>250</v>
+      </c>
+      <c r="F48" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -2188,11 +2192,11 @@
       <c r="D49" t="s">
         <v>176</v>
       </c>
-      <c r="E49" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="F49" s="4" t="s">
-        <v>252</v>
+      <c r="E49" t="s">
+        <v>251</v>
+      </c>
+      <c r="F49" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -2208,11 +2212,11 @@
       <c r="D50" t="s">
         <v>178</v>
       </c>
-      <c r="E50" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="F50" s="4" t="s">
-        <v>253</v>
+      <c r="E50" t="s">
+        <v>252</v>
+      </c>
+      <c r="F50" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -2228,11 +2232,11 @@
       <c r="D51" t="s">
         <v>180</v>
       </c>
-      <c r="E51" s="4" t="s">
-        <v>254</v>
-      </c>
-      <c r="F51" s="4" t="s">
-        <v>254</v>
+      <c r="E51" t="s">
+        <v>253</v>
+      </c>
+      <c r="F51" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -2248,11 +2252,11 @@
       <c r="D52" t="s">
         <v>182</v>
       </c>
-      <c r="E52" s="4" t="s">
-        <v>255</v>
-      </c>
-      <c r="F52" s="4" t="s">
-        <v>255</v>
+      <c r="E52" t="s">
+        <v>254</v>
+      </c>
+      <c r="F52" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -2268,11 +2272,11 @@
       <c r="D53" t="s">
         <v>184</v>
       </c>
-      <c r="E53" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="F53" s="4" t="s">
-        <v>256</v>
+      <c r="E53" t="s">
+        <v>255</v>
+      </c>
+      <c r="F53" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="54" spans="1:6">
@@ -2288,11 +2292,11 @@
       <c r="D54" t="s">
         <v>186</v>
       </c>
-      <c r="E54" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="F54" s="4" t="s">
-        <v>257</v>
+      <c r="E54" t="s">
+        <v>256</v>
+      </c>
+      <c r="F54" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="55" spans="1:6">
@@ -2308,11 +2312,11 @@
       <c r="D55" t="s">
         <v>189</v>
       </c>
-      <c r="E55" s="4" t="s">
-        <v>258</v>
-      </c>
-      <c r="F55" s="4" t="s">
-        <v>258</v>
+      <c r="E55" t="s">
+        <v>257</v>
+      </c>
+      <c r="F55" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="56" spans="1:6">
@@ -2328,11 +2332,11 @@
       <c r="D56" t="s">
         <v>191</v>
       </c>
-      <c r="E56" s="4" t="s">
-        <v>259</v>
-      </c>
-      <c r="F56" s="4" t="s">
-        <v>259</v>
+      <c r="E56" t="s">
+        <v>258</v>
+      </c>
+      <c r="F56" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="57" spans="1:6">
@@ -2348,11 +2352,11 @@
       <c r="D57" t="s">
         <v>193</v>
       </c>
-      <c r="E57" s="4" t="s">
-        <v>260</v>
-      </c>
-      <c r="F57" s="4" t="s">
-        <v>260</v>
+      <c r="E57" t="s">
+        <v>259</v>
+      </c>
+      <c r="F57" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="58" spans="1:6">
@@ -2368,11 +2372,11 @@
       <c r="D58" t="s">
         <v>195</v>
       </c>
-      <c r="E58" s="4" t="s">
-        <v>261</v>
-      </c>
-      <c r="F58" s="4" t="s">
-        <v>261</v>
+      <c r="E58" t="s">
+        <v>260</v>
+      </c>
+      <c r="F58" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -2388,11 +2392,11 @@
       <c r="D59" t="s">
         <v>197</v>
       </c>
-      <c r="E59" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="F59" s="4" t="s">
-        <v>262</v>
+      <c r="E59" t="s">
+        <v>261</v>
+      </c>
+      <c r="F59" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="60" spans="1:6">
@@ -2408,11 +2412,11 @@
       <c r="D60" t="s">
         <v>199</v>
       </c>
-      <c r="E60" s="4" t="s">
-        <v>263</v>
-      </c>
-      <c r="F60" s="4" t="s">
-        <v>263</v>
+      <c r="E60" t="s">
+        <v>262</v>
+      </c>
+      <c r="F60" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="61" spans="1:6">
@@ -2428,14 +2432,19 @@
       <c r="D61" t="s">
         <v>201</v>
       </c>
-      <c r="E61" s="4" t="s">
-        <v>264</v>
-      </c>
-      <c r="F61" s="4" t="s">
-        <v>264</v>
+      <c r="E61" t="s">
+        <v>263</v>
+      </c>
+      <c r="F61" t="s">
+        <v>263</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D2" r:id="rId1" xr:uid="{7EB14442-7F4D-4EA2-A7A3-CED48DD8EC97}"/>
+    <hyperlink ref="E2" r:id="rId2" xr:uid="{06588170-52C7-4692-9A8F-97B1C32FA1E6}"/>
+    <hyperlink ref="F2" r:id="rId3" xr:uid="{84B9E46A-381A-41DC-91CA-7A2C94150F83}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/src/test/resources/testScriptData.xlsx
+++ b/src/test/resources/testScriptData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Automation Testing\Selenium\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94130F06-832A-47C0-9A03-29D01FB75CC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6FCC8E2-2D1A-44E1-B9CD-DF80998324C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E4BAE67D-7837-4FED-B4EB-774E74865D14}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{E4BAE67D-7837-4FED-B4EB-774E74865D14}"/>
   </bookViews>
   <sheets>
     <sheet name="Registration" sheetId="1" r:id="rId1"/>
@@ -2560,6 +2560,7 @@
     <col min="1" max="1" width="25.33203125" customWidth="1"/>
     <col min="2" max="2" width="13.33203125" customWidth="1"/>
     <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="5" max="6" width="18.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
